--- a/site/HR-ITSM-Freshservice-Draft/headings.xlsx
+++ b/site/HR-ITSM-Freshservice-Draft/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Features</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -451,19 +451,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>h_01KV580PQB96710J73V3BG96A9</t>
+          <t>h_01KW1KV946AH1HVN3SVFCJSDWP</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Freshservice-Draft/#h_01KV580PQB96710J73V3BG96A9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Freshservice-Draft/#h_01KW1KV946AH1HVN3SVFCJSDWP</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Monitor</t>
+          <t>Service Desk Bridge</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -473,188 +473,364 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>h_01KHBC8P4Z96NEQJ87YCV9BW5D</t>
+          <t>h_01KW1TH82EGE4EW275DJSB2X28</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Freshservice-Draft/#h_01KHBC8P4Z96NEQJ87YCV9BW5D</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Freshservice-Draft/#h_01KW1TH82EGE4EW275DJSB2X28</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Define Notification Channel</t>
+          <t>Source</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>h_01KSFFXMC8DGHWE6ESQJQQF281</t>
+          <t>h_01KW99M18FJN4C08APNFE610PF</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Freshservice-Draft/#h_01KSFFXMC8DGHWE6ESQJQQF281</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Freshservice-Draft/#h_01KW99M18FJN4C08APNFE610PF</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Notification Configuration</t>
+          <t>Application Settings</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>h_01KV7V6X68TA0NPF6YFYGCPB2N</t>
+          <t>h_01KW99P5MF7JDAS422WSPRXVMP</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Freshservice-Draft/#h_01KV7V6X68TA0NPF6YFYGCPB2N</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Freshservice-Draft/#h_01KW99P5MF7JDAS422WSPRXVMP</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Global Operational Settings</t>
+          <t>Filter Employees</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>h_01KV7VV1J9X30QVYDJQDGBQMRQ</t>
+          <t>h_01KW99TXRPDSKSKEW8YJCQGTNN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Freshservice-Draft/#h_01KV7VV1J9X30QVYDJQDGBQMRQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Freshservice-Draft/#h_01KW99TXRPDSKSKEW8YJCQGTNN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Logging Settings</t>
+          <t>Employee Filter Configuration</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>h_01KV7W4KZY1XFCJ3YSFXQMJHP9</t>
+          <t>h_01KW9CC09AMV3E6K7G5X78EPEV</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Freshservice-Draft/#h_01KV7W4KZY1XFCJ3YSFXQMJHP9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Freshservice-Draft/#h_01KW9CC09AMV3E6K7G5X78EPEV</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>h_01KV86ERRYGWDMSKMK5YKZMPR9</t>
+          <t>h_01KV580PQB96710J73V3BG96A9</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Freshservice-Draft/#h_01KV86ERRYGWDMSKMK5YKZMPR9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Freshservice-Draft/#h_01KV580PQB96710J73V3BG96A9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Log Insight Settings</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>h_01KV86ERRYCD184XX20ETKPWPR</t>
+          <t>h_01KHBC8P4Z96NEQJ87YCV9BW5D</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Freshservice-Draft/#h_01KV86ERRYCD184XX20ETKPWPR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Freshservice-Draft/#h_01KHBC8P4Z96NEQJ87YCV9BW5D</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Define Notification Channel</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>h_01KNS2NCYH8BG3B41F5XYD4P5M</t>
+          <t>h_01KSFFXMC8DGHWE6ESQJQQF281</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Freshservice-Draft/#h_01KNS2NCYH8BG3B41F5XYD4P5M</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Freshservice-Draft/#h_01KSFFXMC8DGHWE6ESQJQQF281</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Notification Configuration</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>h_01KV7V6X68TA0NPF6YFYGCPB2N</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Freshservice-Draft/#h_01KV7V6X68TA0NPF6YFYGCPB2N</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Global Operational Settings</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>h_01KV7VV1J9X30QVYDJQDGBQMRQ</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Freshservice-Draft/#h_01KV7VV1J9X30QVYDJQDGBQMRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Logging Settings</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>h_01KV7W4KZY1XFCJ3YSFXQMJHP9</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Freshservice-Draft/#h_01KV7W4KZY1XFCJ3YSFXQMJHP9</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Report Settings</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>h_01KV86ERRYGWDMSKMK5YKZMPR9</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Freshservice-Draft/#h_01KV86ERRYGWDMSKMK5YKZMPR9</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Log Insight Settings</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>h_01KV86ERRYCD184XX20ETKPWPR</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Freshservice-Draft/#h_01KV86ERRYCD184XX20ETKPWPR</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Execution</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>h_01KNS2NCYH8BG3B41F5XYD4P5M</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Freshservice-Draft/#h_01KNS2NCYH8BG3B41F5XYD4P5M</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>Advanced Settings</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>H4</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>h_01KS28NHEHVRN9BPPCKGXGAYYN</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Freshservice-Draft/#h_01KS28NHEHVRN9BPPCKGXGAYYN</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Freshservice-Draft/#h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>h_01KVWRPTWRN33APTZ4EAFVBT22</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Freshservice-Draft/#h_01KVWRPTWRN33APTZ4EAFVBT22</t>
         </is>
       </c>
     </row>
